--- a/data/trans_camb/P6906-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 24,23</t>
+          <t>0,07; 25,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 24,66</t>
+          <t>-3,25; 23,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 14,28</t>
+          <t>-10,74; 13,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 23,82</t>
+          <t>-8,93; 26,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 38,01</t>
+          <t>-7,95; 38,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 20,32</t>
+          <t>-11,64; 23,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 20,63</t>
+          <t>0,49; 19,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 22,87</t>
+          <t>0,16; 23,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 13,67</t>
+          <t>-7,2; 12,46</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 299,17</t>
+          <t>-8,65; 324,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 264,07</t>
+          <t>-29,19; 279,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 188,27</t>
+          <t>-77,27; 168,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 387,99</t>
+          <t>-54,89; 435,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 507,67</t>
+          <t>-57,41; 666,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 340,23</t>
+          <t>-59,93; 441,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 223,95</t>
+          <t>3,61; 233,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 238,97</t>
+          <t>-2,53; 263,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 160,59</t>
+          <t>-49,34; 139,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 10,01</t>
+          <t>-6,38; 9,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 3,29</t>
+          <t>-11,58; 3,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 1,9</t>
+          <t>-14,14; 1,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 19,07</t>
+          <t>-4,1; 19,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 19,51</t>
+          <t>-2,36; 20,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 7,72</t>
+          <t>-13,13; 8,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 9,9</t>
+          <t>-2,78; 10,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 6,09</t>
+          <t>-6,76; 5,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 2,02</t>
+          <t>-10,19; 2,25</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 50,07</t>
+          <t>-24,22; 46,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 16,01</t>
+          <t>-42,3; 16,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 10,1</t>
+          <t>-52,49; 4,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 106,01</t>
+          <t>-14,58; 108,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 111,69</t>
+          <t>-9,77; 110,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 43,49</t>
+          <t>-44,6; 44,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 47,94</t>
+          <t>-11,01; 50,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 27,84</t>
+          <t>-26,32; 27,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 9,44</t>
+          <t>-38,83; 10,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 17,9</t>
+          <t>-17,02; 19,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 25,3</t>
+          <t>-9,13; 26,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 9,63</t>
+          <t>-21,82; 13,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 27,03</t>
+          <t>-7,94; 25,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 29,38</t>
+          <t>-3,48; 27,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 26,74</t>
+          <t>-1,01; 27,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 16,14</t>
+          <t>-8,88; 16,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 22,93</t>
+          <t>-1,66; 21,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 14,18</t>
+          <t>-6,4; 14,2</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 70,04</t>
+          <t>-42,65; 72,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 96,98</t>
+          <t>-22,04; 104,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 38,29</t>
+          <t>-54,25; 56,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 184,87</t>
+          <t>-27,77; 167,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 191,21</t>
+          <t>-13,47; 192,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 195,16</t>
+          <t>-4,38; 191,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 70,38</t>
+          <t>-27,87; 69,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 101,72</t>
+          <t>-5,22; 92,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 59,5</t>
+          <t>-20,02; 59,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 9,9</t>
+          <t>-3,2; 9,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 7,29</t>
+          <t>-4,95; 7,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 3,09</t>
+          <t>-10,18; 2,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 16,64</t>
+          <t>-1,48; 16,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 19,31</t>
+          <t>2,42; 18,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 11,14</t>
+          <t>-6,08; 10,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 10,09</t>
+          <t>0,12; 10,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 10,02</t>
+          <t>0,3; 10,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 4,46</t>
+          <t>-5,04; 5,28</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 49,47</t>
+          <t>-13,09; 47,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 36,13</t>
+          <t>-19,95; 36,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 15,64</t>
+          <t>-40,04; 14,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 94,27</t>
+          <t>-6,19; 95,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,84; 111,27</t>
+          <t>8,55; 103,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 62,0</t>
+          <t>-23,06; 57,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 49,19</t>
+          <t>0,71; 50,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 50,16</t>
+          <t>1,23; 50,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 21,65</t>
+          <t>-20,61; 26,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6906-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>4,96</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 25,56</t>
+          <t>0,09; 26,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 23,9</t>
+          <t>-2,21; 25,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 13,88</t>
+          <t>-10,03; 17,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 26,07</t>
+          <t>-8,67; 24,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 38,21</t>
+          <t>-5,38; 43,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 23,23</t>
+          <t>-8,26; 25,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 19,77</t>
+          <t>0,25; 20,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 23,05</t>
+          <t>-0,41; 23,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 12,46</t>
+          <t>-4,57; 16,51</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-4,43%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 324,3</t>
+          <t>-7,3; 307,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 279,34</t>
+          <t>-19,18; 311,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,27; 168,12</t>
+          <t>-71,45; 205,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 435,23</t>
+          <t>-48,08; 423,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 666,96</t>
+          <t>-43,09; 795,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 441,05</t>
+          <t>-45,8; 394,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 233,68</t>
+          <t>0,01; 246,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 263,18</t>
+          <t>-7,91; 257,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 139,46</t>
+          <t>-35,03; 180,52</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,48</t>
+          <t>-5,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,97</t>
+          <t>-2,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 9,38</t>
+          <t>-6,18; 10,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 3,02</t>
+          <t>-12,33; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 1,02</t>
+          <t>-12,6; 3,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 19,69</t>
+          <t>-3,39; 18,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 20,3</t>
+          <t>-3,71; 19,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 8,45</t>
+          <t>-8,67; 10,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 10,32</t>
+          <t>-2,6; 10,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,91</t>
+          <t>-5,97; 7,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 2,25</t>
+          <t>-7,95; 3,2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-27,31%</t>
+          <t>-21,69%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-6,17%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,72%</t>
+          <t>-8,82%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 46,58</t>
+          <t>-23,3; 51,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,3; 16,24</t>
+          <t>-44,65; 16,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 4,71</t>
+          <t>-46,08; 16,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 108,83</t>
+          <t>-13,61; 100,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 110,62</t>
+          <t>-13,45; 108,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 44,72</t>
+          <t>-27,82; 64,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 50,87</t>
+          <t>-9,98; 51,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 27,57</t>
+          <t>-22,86; 35,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 10,69</t>
+          <t>-29,52; 15,37</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>-5,38</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,44</t>
+          <t>12,23</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>3,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 19,16</t>
+          <t>-18,48; 17,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 26,06</t>
+          <t>-9,02; 25,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 13,43</t>
+          <t>-21,92; 11,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 25,81</t>
+          <t>-9,41; 26,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 27,77</t>
+          <t>-3,9; 28,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 27,64</t>
+          <t>-3,29; 25,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 16,54</t>
+          <t>-8,12; 17,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 21,57</t>
+          <t>-1,44; 20,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 14,2</t>
+          <t>-6,97; 14,35</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-16,47%</t>
+          <t>-15,82%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 72,37</t>
+          <t>-48,56; 63,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 104,3</t>
+          <t>-21,46; 92,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 56,63</t>
+          <t>-51,75; 45,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 167,12</t>
+          <t>-33,18; 164,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 192,99</t>
+          <t>-15,38; 195,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 191,7</t>
+          <t>-10,54; 173,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 69,43</t>
+          <t>-25,89; 72,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 92,5</t>
+          <t>-5,39; 90,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 59,16</t>
+          <t>-20,46; 63,2</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-2,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>1,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 9,48</t>
+          <t>-2,71; 9,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 7,51</t>
+          <t>-4,98; 7,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 2,9</t>
+          <t>-8,06; 4,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 16,53</t>
+          <t>-0,37; 15,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 18,71</t>
+          <t>3,18; 19,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 10,1</t>
+          <t>-1,49; 12,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 10,34</t>
+          <t>0,39; 10,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 10,21</t>
+          <t>-0,06; 10,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 5,28</t>
+          <t>-3,04; 6,26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-15,68%</t>
+          <t>-10,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,43%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 47,45</t>
+          <t>-11,26; 48,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 36,89</t>
+          <t>-20,05; 38,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 14,13</t>
+          <t>-32,9; 20,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 95,64</t>
+          <t>-2,94; 89,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,55; 103,49</t>
+          <t>11,75; 106,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 57,79</t>
+          <t>-6,09; 71,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 50,61</t>
+          <t>1,38; 53,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 50,3</t>
+          <t>-0,35; 49,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 26,37</t>
+          <t>-11,93; 30,89</t>
         </is>
       </c>
     </row>
